--- a/analise_eua/tecnologia/meta/meta_10q.xlsx
+++ b/analise_eua/tecnologia/meta/meta_10q.xlsx
@@ -433,65 +433,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -502,60 +505,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>15462</v>
+      </c>
+      <c r="C2" t="n">
         <v>23426</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>10187</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>12005</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>28750</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>43852</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>32045</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>32307</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>36890</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>28785</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>11551</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>14308</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>12681</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>14886</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>14496</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>16186</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>19513</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>11617</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>21045</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>23618</v>
       </c>
     </row>
@@ -566,60 +572,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>74798</v>
+      </c>
+      <c r="C3" t="n">
         <v>57754</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>34261</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>35066</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>41480</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>27048</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>26035</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>25813</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>24233</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>24661</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>25888</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>27468</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>27808</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>29004</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>43579</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>47894</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>44706</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>44003</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>37195</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>36671</v>
       </c>
     </row>
@@ -630,60 +639,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>21752</v>
+      </c>
+      <c r="C4" t="n">
         <v>17470</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>17297</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>16561</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>14514</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>14700</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>14505</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>13430</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>12944</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>12511</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>11044</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>11227</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>11525</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>11390</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>12088</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>11698</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>10276</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>8024</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>7483</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>7289</v>
       </c>
     </row>
@@ -694,60 +706,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>13463</v>
+      </c>
+      <c r="C5" t="n">
         <v>11115</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>11373</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>9981</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>5483</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>5467</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3846</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3780</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4311</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>3603</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4000</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>5312</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3973</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3985</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5258</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4919</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2827</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2155</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2407</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1771</v>
       </c>
     </row>
@@ -758,60 +773,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>125475</v>
+      </c>
+      <c r="C6" t="n">
         <v>109765</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>73118</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>73613</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>90227</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>91067</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>76431</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>75330</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>78378</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>69560</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>52483</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>58315</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>55987</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>59265</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>75421</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>80697</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>77322</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>65799</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>68130</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>69349</v>
       </c>
     </row>
@@ -822,60 +840,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>30157</v>
+      </c>
+      <c r="C7" t="n">
         <v>28410</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>25074</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>21988</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>6168</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>6071</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>6207</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>6218</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>6142</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>6208</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>6167</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>6528</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6536</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>6775</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>6758</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>6393</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>6342</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>6164</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,60 +907,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>225724</v>
+      </c>
+      <c r="C8" t="n">
         <v>194776</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>160270</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>147039</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>133567</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>112162</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>102959</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>98908</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>91772</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>87949</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>84156</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>73738</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>67588</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>61582</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>53726</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>50909</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>47720</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>42291</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>39006</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>37127</v>
       </c>
     </row>
@@ -950,60 +974,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>23985</v>
+      </c>
+      <c r="C9" t="n">
         <v>23268</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>17372</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>15662</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>15505</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>14812</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>14058</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>13555</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>13033</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>12955</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>12899</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>13641</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>14130</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>12241</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>11063</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>10525</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>10202</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>9439</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>9429</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>9359</v>
       </c>
     </row>
@@ -1014,13 +1041,13 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>23406</v>
+      </c>
+      <c r="C10" t="n">
         <v>24748</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>21158</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20654</v>
       </c>
       <c r="E10" t="n">
         <v>20654</v>
@@ -1035,39 +1062,42 @@
         <v>20654</v>
       </c>
       <c r="I10" t="n">
+        <v>20654</v>
+      </c>
+      <c r="J10" t="n">
         <v>20668</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>20659</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>20649</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>20268</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>20229</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>19923</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>19065</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>19219</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>19056</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>19031</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>19029</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>18811</v>
       </c>
     </row>
@@ -1078,60 +1108,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>21209</v>
+      </c>
+      <c r="C11" t="n">
         <v>14283</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>6852</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>15788</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>14092</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>11642</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>9929</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>8179</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5468</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>8501</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7188</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>5529</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>4344</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>3522</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>3187</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>2352</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>2376</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>2969</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>3238</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2887</v>
       </c>
     </row>
@@ -1142,421 +1175,439 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>449956</v>
+      </c>
+      <c r="C12" t="n">
         <v>395250</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>303844</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>294744</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>280213</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>256408</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>230238</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>222844</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>216274</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>206688</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>184491</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>178894</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>169779</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>164218</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>169585</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>170609</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>163523</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>146437</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>139691</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>138371</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payable, Trade, Current</t>
+          <t>Operating Lease, Current</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13326</v>
+        <v>2425</v>
       </c>
       <c r="C13" t="n">
-        <v>7798</v>
+        <v>2414</v>
       </c>
       <c r="D13" t="n">
-        <v>10271</v>
+        <v>2113</v>
       </c>
       <c r="E13" t="n">
-        <v>8512</v>
+        <v>1977</v>
       </c>
       <c r="F13" t="n">
-        <v>7656</v>
+        <v>1976</v>
       </c>
       <c r="G13" t="n">
-        <v>3173</v>
+        <v>2016</v>
       </c>
       <c r="H13" t="n">
-        <v>3785</v>
+        <v>1917</v>
       </c>
       <c r="I13" t="n">
-        <v>4372</v>
+        <v>1676</v>
       </c>
       <c r="J13" t="n">
-        <v>3093</v>
+        <v>1460</v>
       </c>
       <c r="K13" t="n">
-        <v>3672</v>
+        <v>1396</v>
       </c>
       <c r="L13" t="n">
-        <v>3871</v>
+        <v>1479</v>
       </c>
       <c r="M13" t="n">
-        <v>4008</v>
+        <v>1291</v>
       </c>
       <c r="N13" t="n">
-        <v>3246</v>
+        <v>1275</v>
       </c>
       <c r="O13" t="n">
-        <v>2195</v>
+        <v>1159</v>
       </c>
       <c r="P13" t="n">
-        <v>973</v>
+        <v>1086</v>
       </c>
       <c r="Q13" t="n">
-        <v>878</v>
+        <v>1051</v>
       </c>
       <c r="R13" t="n">
-        <v>1106</v>
+        <v>1040</v>
       </c>
       <c r="S13" t="n">
-        <v>920</v>
+        <v>975</v>
       </c>
       <c r="T13" t="n">
-        <v>712</v>
+        <v>899</v>
+      </c>
+      <c r="U13" t="n">
+        <v>835</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Current</t>
+          <t>Accrued Liabilities, Current</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2414</v>
+        <v>38065</v>
       </c>
       <c r="C14" t="n">
-        <v>2113</v>
+        <v>31013</v>
       </c>
       <c r="D14" t="n">
-        <v>1977</v>
+        <v>27047</v>
       </c>
       <c r="E14" t="n">
-        <v>1976</v>
+        <v>25057</v>
       </c>
       <c r="F14" t="n">
-        <v>2016</v>
+        <v>23402</v>
       </c>
       <c r="G14" t="n">
-        <v>1917</v>
+        <v>23658</v>
       </c>
       <c r="H14" t="n">
-        <v>1676</v>
+        <v>21914</v>
       </c>
       <c r="I14" t="n">
-        <v>1460</v>
+        <v>22640</v>
       </c>
       <c r="J14" t="n">
-        <v>1396</v>
+        <v>23929</v>
       </c>
       <c r="K14" t="n">
-        <v>1479</v>
+        <v>24660</v>
       </c>
       <c r="L14" t="n">
-        <v>1291</v>
+        <v>19345</v>
       </c>
       <c r="M14" t="n">
-        <v>1275</v>
+        <v>16036</v>
       </c>
       <c r="N14" t="n">
-        <v>1159</v>
+        <v>15420</v>
       </c>
       <c r="O14" t="n">
-        <v>1086</v>
+        <v>15226</v>
       </c>
       <c r="P14" t="n">
-        <v>1051</v>
+        <v>13158</v>
       </c>
       <c r="Q14" t="n">
-        <v>1040</v>
+        <v>11510</v>
       </c>
       <c r="R14" t="n">
-        <v>975</v>
+        <v>9411</v>
       </c>
       <c r="S14" t="n">
-        <v>899</v>
+        <v>8684</v>
       </c>
       <c r="T14" t="n">
-        <v>835</v>
+        <v>8496</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12446</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Accrued Liabilities, Current</t>
+          <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31013</v>
+        <v>56379</v>
       </c>
       <c r="C15" t="n">
-        <v>27047</v>
+        <v>46753</v>
       </c>
       <c r="D15" t="n">
-        <v>25057</v>
+        <v>36958</v>
       </c>
       <c r="E15" t="n">
-        <v>23402</v>
+        <v>37305</v>
       </c>
       <c r="F15" t="n">
-        <v>23658</v>
+        <v>33890</v>
       </c>
       <c r="G15" t="n">
-        <v>21914</v>
+        <v>33330</v>
       </c>
       <c r="H15" t="n">
-        <v>22640</v>
+        <v>27004</v>
       </c>
       <c r="I15" t="n">
-        <v>23929</v>
+        <v>28101</v>
       </c>
       <c r="J15" t="n">
-        <v>24660</v>
+        <v>30531</v>
       </c>
       <c r="K15" t="n">
-        <v>19345</v>
+        <v>29921</v>
       </c>
       <c r="L15" t="n">
-        <v>16036</v>
+        <v>25381</v>
       </c>
       <c r="M15" t="n">
-        <v>15420</v>
+        <v>22687</v>
       </c>
       <c r="N15" t="n">
-        <v>15226</v>
+        <v>22217</v>
       </c>
       <c r="O15" t="n">
-        <v>13158</v>
+        <v>21086</v>
       </c>
       <c r="P15" t="n">
-        <v>11510</v>
+        <v>17812</v>
       </c>
       <c r="Q15" t="n">
-        <v>9411</v>
+        <v>14874</v>
       </c>
       <c r="R15" t="n">
-        <v>8684</v>
+        <v>12717</v>
       </c>
       <c r="S15" t="n">
-        <v>8496</v>
+        <v>11944</v>
       </c>
       <c r="T15" t="n">
-        <v>12446</v>
+        <v>11308</v>
+      </c>
+      <c r="U15" t="n">
+        <v>15069</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Liabilities, Current</t>
+          <t>Operating Lease, Noncurrent</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46753</v>
+        <v>26229</v>
       </c>
       <c r="C16" t="n">
-        <v>36958</v>
+        <v>25607</v>
       </c>
       <c r="D16" t="n">
-        <v>37305</v>
+        <v>20113</v>
       </c>
       <c r="E16" t="n">
-        <v>33890</v>
+        <v>18751</v>
       </c>
       <c r="F16" t="n">
-        <v>33330</v>
+        <v>18714</v>
       </c>
       <c r="G16" t="n">
-        <v>27004</v>
+        <v>18208</v>
       </c>
       <c r="H16" t="n">
-        <v>28101</v>
+        <v>17685</v>
       </c>
       <c r="I16" t="n">
-        <v>30531</v>
+        <v>17570</v>
       </c>
       <c r="J16" t="n">
-        <v>29921</v>
+        <v>16374</v>
       </c>
       <c r="K16" t="n">
-        <v>25381</v>
+        <v>16440</v>
       </c>
       <c r="L16" t="n">
-        <v>22687</v>
+        <v>16171</v>
       </c>
       <c r="M16" t="n">
-        <v>22217</v>
+        <v>14687</v>
       </c>
       <c r="N16" t="n">
-        <v>21086</v>
+        <v>14792</v>
       </c>
       <c r="O16" t="n">
-        <v>17812</v>
+        <v>12894</v>
       </c>
       <c r="P16" t="n">
-        <v>14874</v>
+        <v>11554</v>
       </c>
       <c r="Q16" t="n">
-        <v>12717</v>
+        <v>10956</v>
       </c>
       <c r="R16" t="n">
-        <v>11944</v>
+        <v>10574</v>
       </c>
       <c r="S16" t="n">
-        <v>11308</v>
+        <v>9641</v>
       </c>
       <c r="T16" t="n">
-        <v>15069</v>
+        <v>9633</v>
+      </c>
+      <c r="U16" t="n">
+        <v>9509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Noncurrent</t>
+          <t>Long-term Debt</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25607</v>
+        <v>83664</v>
       </c>
       <c r="C17" t="n">
-        <v>20113</v>
+        <v>58748</v>
       </c>
       <c r="D17" t="n">
-        <v>18751</v>
+        <v>28834</v>
       </c>
       <c r="E17" t="n">
-        <v>18714</v>
+        <v>28832</v>
       </c>
       <c r="F17" t="n">
-        <v>18208</v>
+        <v>28829</v>
       </c>
       <c r="G17" t="n">
-        <v>17685</v>
+        <v>28823</v>
       </c>
       <c r="H17" t="n">
-        <v>17570</v>
+        <v>18389</v>
       </c>
       <c r="I17" t="n">
-        <v>16374</v>
+        <v>18387</v>
       </c>
       <c r="J17" t="n">
-        <v>16440</v>
+        <v>18383</v>
       </c>
       <c r="K17" t="n">
-        <v>16171</v>
+        <v>18382</v>
       </c>
       <c r="L17" t="n">
-        <v>14687</v>
+        <v>9925</v>
       </c>
       <c r="M17" t="n">
-        <v>14792</v>
+        <v>9922</v>
       </c>
       <c r="N17" t="n">
-        <v>12894</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>11554</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10956</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10574</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>9641</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>9633</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>9509</v>
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Long-term Debt</t>
+          <t>Accrued Income Taxes, Noncurrent</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58748</v>
+        <v>18326</v>
       </c>
       <c r="C18" t="n">
-        <v>28834</v>
+        <v>16849</v>
       </c>
       <c r="D18" t="n">
-        <v>28832</v>
+        <v>11738</v>
       </c>
       <c r="E18" t="n">
-        <v>28829</v>
+        <v>12046</v>
       </c>
       <c r="F18" t="n">
-        <v>28823</v>
+        <v>10991</v>
       </c>
       <c r="G18" t="n">
-        <v>18389</v>
+        <v>9171</v>
       </c>
       <c r="H18" t="n">
-        <v>18387</v>
+        <v>7897</v>
       </c>
       <c r="I18" t="n">
-        <v>18383</v>
+        <v>7795</v>
       </c>
       <c r="J18" t="n">
-        <v>18382</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>9925</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9922</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1580,455 +1631,479 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Accrued Income Taxes, Noncurrent</t>
+          <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16849</v>
+        <v>4137</v>
       </c>
       <c r="C19" t="n">
-        <v>11738</v>
+        <v>3612</v>
       </c>
       <c r="D19" t="n">
-        <v>12046</v>
+        <v>12135</v>
       </c>
       <c r="E19" t="n">
-        <v>10991</v>
+        <v>2740</v>
       </c>
       <c r="F19" t="n">
-        <v>9171</v>
+        <v>2760</v>
       </c>
       <c r="G19" t="n">
-        <v>7897</v>
+        <v>2347</v>
       </c>
       <c r="H19" t="n">
-        <v>7795</v>
+        <v>2500</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1462</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>8113</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>7912</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8219</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7504</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7003</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7010</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6859</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6552</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6575</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>7121</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>8303</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8489</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Other Liabilities, Noncurrent</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3612</v>
+        <v>188735</v>
       </c>
       <c r="C20" t="n">
-        <v>12135</v>
+        <v>151569</v>
       </c>
       <c r="D20" t="n">
-        <v>2740</v>
+        <v>109778</v>
       </c>
       <c r="E20" t="n">
-        <v>2760</v>
+        <v>99674</v>
       </c>
       <c r="F20" t="n">
-        <v>2347</v>
+        <v>95184</v>
       </c>
       <c r="G20" t="n">
-        <v>2500</v>
+        <v>91879</v>
       </c>
       <c r="H20" t="n">
-        <v>1462</v>
+        <v>73475</v>
       </c>
       <c r="I20" t="n">
-        <v>8113</v>
+        <v>73315</v>
       </c>
       <c r="J20" t="n">
-        <v>7912</v>
+        <v>73401</v>
       </c>
       <c r="K20" t="n">
-        <v>8219</v>
+        <v>72655</v>
       </c>
       <c r="L20" t="n">
-        <v>7504</v>
+        <v>59696</v>
       </c>
       <c r="M20" t="n">
-        <v>7003</v>
+        <v>54800</v>
       </c>
       <c r="N20" t="n">
-        <v>7010</v>
+        <v>44012</v>
       </c>
       <c r="O20" t="n">
-        <v>6859</v>
+        <v>40990</v>
       </c>
       <c r="P20" t="n">
-        <v>6552</v>
+        <v>36225</v>
       </c>
       <c r="Q20" t="n">
-        <v>6575</v>
+        <v>32382</v>
       </c>
       <c r="R20" t="n">
-        <v>7121</v>
+        <v>29866</v>
       </c>
       <c r="S20" t="n">
-        <v>8303</v>
+        <v>28706</v>
       </c>
       <c r="T20" t="n">
-        <v>8489</v>
+        <v>29244</v>
+      </c>
+      <c r="U20" t="n">
+        <v>33067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Common Stocks, Including Additional Paid in Capital</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151569</v>
+        <v>103981</v>
       </c>
       <c r="C21" t="n">
-        <v>109778</v>
+        <v>99337</v>
       </c>
       <c r="D21" t="n">
-        <v>99674</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>95184</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>91879</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>73475</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>73315</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>73401</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>72655</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>59696</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>54800</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>44012</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>40990</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>36225</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>32382</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29866</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>28706</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>29244</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>33067</v>
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Common Stocks, Including Additional Paid in Capital</t>
+          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>99337</v>
+        <v>-603</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-303</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-1865</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1192</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-2695</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-2655</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-3556</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-3106</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-2981</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-5054</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-3411</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1996</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-207</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-142</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-544</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
+          <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-303</v>
+        <v>157843</v>
       </c>
       <c r="C23" t="n">
-        <v>159</v>
+        <v>144647</v>
       </c>
       <c r="D23" t="n">
-        <v>229</v>
+        <v>101577</v>
       </c>
       <c r="E23" t="n">
-        <v>-1865</v>
+        <v>106345</v>
       </c>
       <c r="F23" t="n">
-        <v>-1192</v>
+        <v>101326</v>
       </c>
       <c r="G23" t="n">
-        <v>-2695</v>
+        <v>84972</v>
       </c>
       <c r="H23" t="n">
-        <v>-2655</v>
+        <v>81188</v>
       </c>
       <c r="I23" t="n">
-        <v>-3556</v>
+        <v>76793</v>
       </c>
       <c r="J23" t="n">
-        <v>-3106</v>
+        <v>75205</v>
       </c>
       <c r="K23" t="n">
-        <v>-2981</v>
+        <v>67980</v>
       </c>
       <c r="L23" t="n">
-        <v>-5054</v>
+        <v>61241</v>
       </c>
       <c r="M23" t="n">
-        <v>-3411</v>
+        <v>67056</v>
       </c>
       <c r="N23" t="n">
-        <v>-1996</v>
+        <v>69249</v>
       </c>
       <c r="O23" t="n">
-        <v>-207</v>
+        <v>67712</v>
       </c>
       <c r="P23" t="n">
-        <v>285</v>
+        <v>79233</v>
       </c>
       <c r="Q23" t="n">
-        <v>154</v>
+        <v>85097</v>
       </c>
       <c r="R23" t="n">
-        <v>308</v>
+        <v>82343</v>
       </c>
       <c r="S23" t="n">
-        <v>-142</v>
+        <v>68513</v>
       </c>
       <c r="T23" t="n">
-        <v>-544</v>
+        <v>62784</v>
+      </c>
+      <c r="U23" t="n">
+        <v>59160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Retained Earnings (Accumulated Deficit)</t>
+          <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>144647</v>
+        <v>261221</v>
       </c>
       <c r="C24" t="n">
-        <v>101577</v>
+        <v>243681</v>
       </c>
       <c r="D24" t="n">
-        <v>106345</v>
+        <v>194066</v>
       </c>
       <c r="E24" t="n">
-        <v>101326</v>
+        <v>195070</v>
       </c>
       <c r="F24" t="n">
-        <v>84972</v>
+        <v>185029</v>
       </c>
       <c r="G24" t="n">
-        <v>81188</v>
+        <v>164529</v>
       </c>
       <c r="H24" t="n">
-        <v>76793</v>
+        <v>156763</v>
       </c>
       <c r="I24" t="n">
-        <v>75205</v>
+        <v>149529</v>
       </c>
       <c r="J24" t="n">
-        <v>67980</v>
+        <v>142873</v>
       </c>
       <c r="K24" t="n">
-        <v>61241</v>
+        <v>134033</v>
       </c>
       <c r="L24" t="n">
-        <v>67056</v>
+        <v>124795</v>
       </c>
       <c r="M24" t="n">
-        <v>69249</v>
+        <v>124094</v>
       </c>
       <c r="N24" t="n">
-        <v>67712</v>
+        <v>125767</v>
       </c>
       <c r="O24" t="n">
-        <v>79233</v>
+        <v>123228</v>
       </c>
       <c r="P24" t="n">
-        <v>85097</v>
+        <v>133360</v>
       </c>
       <c r="Q24" t="n">
-        <v>82343</v>
+        <v>138227</v>
       </c>
       <c r="R24" t="n">
-        <v>68513</v>
+        <v>133657</v>
       </c>
       <c r="S24" t="n">
-        <v>62784</v>
+        <v>117731</v>
       </c>
       <c r="T24" t="n">
-        <v>59160</v>
+        <v>110447</v>
+      </c>
+      <c r="U24" t="n">
+        <v>105304</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Total Shareholders Equity</t>
+          <t>Accounts Payable, Trade, Current</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>243681</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>194066</v>
+        <v>13326</v>
       </c>
       <c r="D25" t="n">
-        <v>195070</v>
+        <v>7798</v>
       </c>
       <c r="E25" t="n">
-        <v>185029</v>
+        <v>10271</v>
       </c>
       <c r="F25" t="n">
-        <v>164529</v>
+        <v>8512</v>
       </c>
       <c r="G25" t="n">
-        <v>156763</v>
+        <v>7656</v>
       </c>
       <c r="H25" t="n">
-        <v>149529</v>
+        <v>3173</v>
       </c>
       <c r="I25" t="n">
-        <v>142873</v>
+        <v>3785</v>
       </c>
       <c r="J25" t="n">
-        <v>134033</v>
+        <v>4372</v>
       </c>
       <c r="K25" t="n">
-        <v>124795</v>
+        <v>3093</v>
       </c>
       <c r="L25" t="n">
-        <v>124094</v>
+        <v>3672</v>
       </c>
       <c r="M25" t="n">
-        <v>125767</v>
+        <v>3871</v>
       </c>
       <c r="N25" t="n">
-        <v>123228</v>
+        <v>4008</v>
       </c>
       <c r="O25" t="n">
-        <v>133360</v>
+        <v>3246</v>
       </c>
       <c r="P25" t="n">
-        <v>138227</v>
+        <v>2195</v>
       </c>
       <c r="Q25" t="n">
-        <v>133657</v>
+        <v>973</v>
       </c>
       <c r="R25" t="n">
-        <v>117731</v>
+        <v>878</v>
       </c>
       <c r="S25" t="n">
-        <v>110447</v>
+        <v>1106</v>
       </c>
       <c r="T25" t="n">
-        <v>105304</v>
+        <v>920</v>
+      </c>
+      <c r="U25" t="n">
+        <v>712</v>
       </c>
     </row>
     <row r="26">
@@ -2041,57 +2116,60 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
         <v>92330</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>88496</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>85568</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>80749</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>78270</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>75391</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>71224</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>69159</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>66535</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>62092</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>59929</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>57512</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>54334</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>52845</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>51160</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>48910</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>47805</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>46688</v>
       </c>
     </row>
@@ -2123,39 +2201,42 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>813</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>856</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>949</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>875</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>965</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>910</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>365</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>514</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>505</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>744</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>859</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>838</v>
       </c>
     </row>
@@ -2187,39 +2268,42 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>770</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>772</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>885</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>975</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>982</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>935</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>909</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>949</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>1006</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>800</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>729</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2260,30 +2344,33 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>514</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>532</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>520</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>464</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>391</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>382</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>379</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>264</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>247</v>
       </c>
     </row>
@@ -2298,65 +2385,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -2367,60 +2457,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>60801</v>
+      </c>
+      <c r="C2" t="n">
         <v>56311</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>51242</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>47516</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>42314</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>40589</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>39071</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>36455</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>34146</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>31999</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>28645</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>27714</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>28822</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>27908</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>29010</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>29077</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>26171</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>21470</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>18687</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>17737</v>
       </c>
     </row>
@@ -2431,60 +2524,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>11330</v>
+      </c>
+      <c r="C3" t="n">
         <v>10218</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>9206</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8491</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7572</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>7375</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7308</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>6640</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6210</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5945</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6108</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>5716</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5192</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>6005</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5771</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>5399</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>5131</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>4194</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3829</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3459</v>
       </c>
     </row>
@@ -2495,60 +2591,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>21656</v>
+      </c>
+      <c r="C4" t="n">
         <v>17699</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>15144</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>12942</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>12150</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>11177</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10537</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>9978</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9241</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>9344</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>9381</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>9170</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>8690</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>7707</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>6316</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>6096</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>5197</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>4763</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>4462</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>4015</v>
       </c>
     </row>
@@ -2559,60 +2658,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="C5" t="n">
         <v>2908</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>2845</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2979</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2757</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2822</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>2721</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2564</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2877</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>3154</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>3044</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>3780</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3595</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3312</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3554</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3259</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2843</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2683</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2840</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>2787</v>
       </c>
     </row>
@@ -2623,60 +2725,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>5609</v>
+      </c>
+      <c r="C6" t="n">
         <v>2614</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>3512</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2663</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2280</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1865</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3658</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>3455</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>2070</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>4164</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2885</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>3384</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2987</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2360</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2946</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>1956</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1622</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1790</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1593</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1583</v>
       </c>
     </row>
@@ -2687,60 +2792,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>42026</v>
+      </c>
+      <c r="C7" t="n">
         <v>33439</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>30707</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>27075</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>24759</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>23239</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>24224</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>22637</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>20398</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>22607</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>21418</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>22050</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>20464</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>19384</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>18587</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>16710</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>14793</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>13430</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>12724</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>11844</v>
       </c>
     </row>
@@ -2751,60 +2859,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>18775</v>
+      </c>
+      <c r="C8" t="n">
         <v>22872</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>20535</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>20441</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>17555</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>17350</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>14847</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>13818</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>13748</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>9392</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>7227</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5664</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>8358</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>8524</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10423</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>12367</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>11378</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>8040</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>5963</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>5893</v>
       </c>
     </row>
@@ -2815,60 +2926,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-19</v>
+      </c>
+      <c r="C9" t="n">
         <v>-1120</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1128</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>93</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>827</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>472</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>259</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>365</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>272</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-99</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>80</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-88</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-172</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>384</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>142</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>146</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>125</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>93</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>168</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -2879,60 +2993,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>18756</v>
+      </c>
+      <c r="C10" t="n">
         <v>21752</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>21663</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>20534</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>18382</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>17822</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>15106</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>14183</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>14020</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>9293</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>7307</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>5576</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>8186</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>8908</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>10565</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>12513</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>11503</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>8133</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>6131</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2943,60 +3060,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2908</v>
+      </c>
+      <c r="C11" t="n">
         <v>-5021</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>18954</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>2197</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1738</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>2134</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1641</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1814</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2437</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1505</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1598</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1181</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1499</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>1443</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1371</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>2119</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>2006</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>287</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>953</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>959</v>
       </c>
     </row>
@@ -3007,60 +3127,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>15848</v>
+      </c>
+      <c r="C12" t="n">
         <v>26773</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>2709</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>18337</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>16644</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>15688</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>13465</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>12369</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>11583</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>7788</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>5709</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>4395</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>6687</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>7465</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>9194</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>10394</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>9497</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>7846</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>5178</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>4902</v>
       </c>
     </row>
@@ -3071,60 +3194,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="C13" t="n">
         <v>10.57</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1.08</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>7.28</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>6.59</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>6.2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.31</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>4.86</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>4.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>3.03</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>2.21</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1.64</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2.47</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.74</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>3.27</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.67</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>3.34</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>2.75</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>1.82</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.72</v>
       </c>
     </row>
@@ -3135,60 +3261,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="C14" t="n">
         <v>10.44</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1.05</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>7.14</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>6.43</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>6.03</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>5.16</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>4.71</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>4.39</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2.98</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2.2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1.64</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2.46</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.72</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3.22</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.61</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>3.3</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>2.71</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.8</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.71</v>
       </c>
     </row>
@@ -3199,60 +3328,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2543</v>
+      </c>
+      <c r="C15" t="n">
         <v>2534</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>2517</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>2518</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>2527</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2529</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2534</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>2545</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>2576</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>2568</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>2587</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2682</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>2704</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2725</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>2814</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>2834</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2847</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2850</v>
       </c>
       <c r="S15" t="n">
         <v>2850</v>
       </c>
       <c r="T15" t="n">
+        <v>2850</v>
+      </c>
+      <c r="U15" t="n">
         <v>2851</v>
       </c>
     </row>
@@ -3263,60 +3395,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2566</v>
+      </c>
+      <c r="C16" t="n">
         <v>2564</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>2572</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>2570</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>2590</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>2600</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>2610</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2625</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>2641</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>2612</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>2596</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2687</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>2713</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2742</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>2859</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>2877</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>2882</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>2891</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>2879</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>2868</v>
       </c>
     </row>
@@ -3357,30 +3492,33 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>3134</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3351</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2498</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>2379</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>2548</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>1830</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>1722</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>1695</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1335</v>
       </c>
     </row>
@@ -3395,65 +3533,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -3464,60 +3605,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>42621</v>
+      </c>
+      <c r="C2" t="n">
         <v>26773</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>37690</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>34981</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>16644</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>41522</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>25834</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>12369</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>25081</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>13498</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>5709</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>18547</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>14152</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7465</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>29085</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>19892</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9497</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>17927</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>10081</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>4902</v>
       </c>
     </row>
@@ -3528,60 +3672,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>12355</v>
+      </c>
+      <c r="C3" t="n">
         <v>5999</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>13205</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8242</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3900</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>11038</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7011</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3374</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>8006</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5147</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>2524</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>6310</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>4135</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2156</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5953</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3958</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1972</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>4999</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3301</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1597</v>
       </c>
     </row>
@@ -3592,60 +3739,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>13690</v>
+      </c>
+      <c r="C4" t="n">
         <v>6032</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>14537</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>8981</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>4147</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>12428</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>8178</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>3562</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>10603</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>7111</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>3051</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>8984</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5850</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2498</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>6757</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>4379</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1830</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>4752</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3030</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1335</v>
       </c>
     </row>
@@ -3656,60 +3806,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1568</v>
+      </c>
+      <c r="C5" t="n">
         <v>123</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>17704</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-2163</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-993</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-3406</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-2098</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-456</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1292</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-1757</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-620</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-2113</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-1016</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-563</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-139</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>647</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>418</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>-816</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>690</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>477</v>
       </c>
     </row>
@@ -3720,11 +3873,11 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1185</v>
+      </c>
+      <c r="C6" t="n">
         <v>1075</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
@@ -3774,6 +3927,9 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3784,60 +3940,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-73</v>
+      </c>
+      <c r="C7" t="n">
         <v>-17</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>-453</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>-430</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-231</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-82</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-71</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-66</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>278</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>204</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-7</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>71</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>-33</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-221</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-161</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-88</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-66</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>56</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>49</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3848,60 +4007,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-2273</v>
+      </c>
+      <c r="C8" t="n">
         <v>2128</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>660</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1466</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2804</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1493</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1350</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2520</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>444</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1122</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>2546</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1930</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2035</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2557</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-1072</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-517</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>849</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1547</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1924</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>2046</v>
       </c>
     </row>
@@ -3912,60 +4074,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-3230</v>
+      </c>
+      <c r="C9" t="n">
         <v>-2424</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-348</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>686</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>360</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-168</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>16</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>100</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-141</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>767</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>821</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-693</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>138</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>573</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-2566</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-2313</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-461</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-89</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-353</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -3976,60 +4141,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-2535</v>
+      </c>
+      <c r="C10" t="n">
         <v>-1082</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-209</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-242</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-52</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-70</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-41</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-94</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>31</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>67</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>30</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-160</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-132</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-108</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-184</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-195</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-10</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-8</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-15</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -4040,60 +4208,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-354</v>
+      </c>
+      <c r="C11" t="n">
         <v>-937</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-637</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-574</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-1034</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-195</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-862</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-1112</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-543</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-1155</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-1104</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-666</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-645</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-882</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>560</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-134</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>-250</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>39</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-100</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-44</v>
       </c>
     </row>
@@ -4104,60 +4275,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>5662</v>
+      </c>
+      <c r="C12" t="n">
         <v>-271</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-2883</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-3338</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-2231</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-1199</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-1771</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-1274</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5702</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>5624</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>334</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2942</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1943</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>763</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>895</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-200</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-1681</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>-3273</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-3016</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>980</v>
       </c>
     </row>
@@ -4168,60 +4342,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-4528</v>
+      </c>
+      <c r="C13" t="n">
         <v>-5173</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>868</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1604</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>712</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1691</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>790</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>83</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-39</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>33</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>184</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>446</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-94</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-5</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>527</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>184</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>210</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-438</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-554</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-68</v>
       </c>
     </row>
@@ -4232,60 +4409,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>64088</v>
+      </c>
+      <c r="C14" t="n">
         <v>32226</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>79586</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>49587</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>24026</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>63340</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>38616</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>19246</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>51709</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>31307</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>13998</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>35964</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>26272</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>14076</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>39579</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>25489</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>12242</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>24707</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>14878</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>11001</v>
       </c>
     </row>
@@ -4296,60 +4476,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-49113</v>
+      </c>
+      <c r="C15" t="n">
         <v>-18997</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-48308</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-29479</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-12941</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-22831</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-14573</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-6400</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-19601</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-13058</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-6842</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-22388</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-13013</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-5441</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-13198</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>-8884</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-4272</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-10502</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-6813</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-3558</v>
       </c>
     </row>
@@ -4360,60 +4543,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-75592</v>
+      </c>
+      <c r="C16" t="n">
         <v>-32978</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>-22349</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>-19509</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-11763</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-14644</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-10176</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-6887</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-1810</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-803</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-85</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-8885</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-6288</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-4068</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>-24314</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>-16528</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>-6231</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>-28193</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-14063</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-7884</v>
       </c>
     </row>
@@ -4424,60 +4610,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>44036</v>
+      </c>
+      <c r="C17" t="n">
         <v>19176</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>23761</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>19057</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>4784</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>11972</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>7858</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>4625</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>3825</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2351</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>534</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1562</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>913</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>402</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>9318</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>6327</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>3981</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>10725</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>7868</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>4644</v>
       </c>
     </row>
@@ -4488,17 +4677,17 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-1670</v>
+      </c>
+      <c r="C18" t="n">
         <v>-544</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-18260</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-15214</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
@@ -4542,6 +4731,9 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4552,17 +4744,17 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-674</v>
+      </c>
+      <c r="C19" t="n">
         <v>-118</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>-1797</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>-775</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
@@ -4606,6 +4798,9 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4616,60 +4811,63 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-474</v>
+      </c>
+      <c r="C20" t="n">
         <v>-372</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-815</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-62</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>-261</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-129</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-72</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-565</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-527</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-444</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-1250</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-1216</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-853</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-330</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>-259</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>-384</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-372</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-33</v>
       </c>
     </row>
@@ -4680,60 +4878,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>156</v>
+      </c>
+      <c r="C21" t="n">
         <v>155</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-48</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>14</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-90</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>112</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-12</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>-20</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-10</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>75</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-1</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-17</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-10</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-160</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-62</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-2</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>-9</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-288</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>-42</v>
       </c>
     </row>
@@ -4744,60 +4945,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>-83331</v>
+      </c>
+      <c r="C22" t="n">
         <v>-33678</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>-67816</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-45968</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-20010</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>-25652</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-17032</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-8734</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-18023</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-11946</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-6743</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-21439</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-11738</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-4779</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-13399</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>-13069</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-4874</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>-24886</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-8287</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>-4109</v>
       </c>
     </row>
@@ -4808,60 +5012,63 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-8704</v>
+      </c>
+      <c r="C23" t="n">
         <v>-4423</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-14128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>-8993</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-4883</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>-9913</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-6370</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-3162</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-4789</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>-2701</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-1009</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-2938</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-1927</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>-925</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>-4007</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>-2432</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>-1077</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>-2444</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-1444</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-690</v>
       </c>
     </row>
@@ -4875,57 +5082,60 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>-26248</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>-22921</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-12754</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-30125</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-21307</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-15008</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-13832</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-10263</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-9365</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-21093</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>-14739</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-9506</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-24476</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>-11018</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>-3939</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>-4343</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-2618</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1250</v>
       </c>
     </row>
@@ -4936,29 +5146,29 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>-2699</v>
+      </c>
+      <c r="C25" t="n">
         <v>-1346</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>-3986</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-2656</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-1329</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-3802</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-2539</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-1273</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -4990,760 +5200,796 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Finance Lease, Principal Payments</t>
+          <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-843</v>
+        <v>24910</v>
       </c>
       <c r="C26" t="n">
-        <v>-1770</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1225</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-751</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-1558</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-614</v>
+        <v>10432</v>
       </c>
       <c r="H26" t="n">
-        <v>-315</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-751</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-484</v>
+        <v>8455</v>
       </c>
       <c r="K26" t="n">
-        <v>-264</v>
+        <v>8455</v>
       </c>
       <c r="L26" t="n">
-        <v>-615</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-452</v>
+        <v>9921</v>
       </c>
       <c r="N26" t="n">
-        <v>-233</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>-505</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-274</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-398</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-209</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Finance Lease, Principal Payments</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59</v>
+        <v>-1805</v>
       </c>
       <c r="C27" t="n">
-        <v>613</v>
+        <v>-843</v>
       </c>
       <c r="D27" t="n">
-        <v>323</v>
+        <v>-1770</v>
       </c>
       <c r="E27" t="n">
-        <v>222</v>
+        <v>-1225</v>
       </c>
       <c r="F27" t="n">
-        <v>-350</v>
+        <v>-751</v>
       </c>
       <c r="G27" t="n">
-        <v>-115</v>
+        <v>-1558</v>
       </c>
       <c r="H27" t="n">
-        <v>-9</v>
+        <v>-614</v>
       </c>
       <c r="I27" t="n">
-        <v>-182</v>
+        <v>-315</v>
       </c>
       <c r="J27" t="n">
-        <v>-231</v>
+        <v>-751</v>
       </c>
       <c r="K27" t="n">
-        <v>122</v>
+        <v>-484</v>
       </c>
       <c r="L27" t="n">
-        <v>-101</v>
+        <v>-264</v>
       </c>
       <c r="M27" t="n">
-        <v>-46</v>
+        <v>-615</v>
       </c>
       <c r="N27" t="n">
-        <v>-16</v>
+        <v>-452</v>
       </c>
       <c r="O27" t="n">
-        <v>-13</v>
+        <v>-233</v>
       </c>
       <c r="P27" t="n">
-        <v>-13</v>
+        <v>-505</v>
       </c>
       <c r="Q27" t="n">
-        <v>32</v>
+        <v>-274</v>
       </c>
       <c r="R27" t="n">
-        <v>124</v>
+        <v>-151</v>
       </c>
       <c r="S27" t="n">
-        <v>114</v>
+        <v>-398</v>
       </c>
       <c r="T27" t="n">
-        <v>98</v>
+        <v>-209</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-6553</v>
+        <v>-2288</v>
       </c>
       <c r="C28" t="n">
-        <v>-45519</v>
+        <v>59</v>
       </c>
       <c r="D28" t="n">
-        <v>-35472</v>
+        <v>613</v>
       </c>
       <c r="E28" t="n">
-        <v>-19495</v>
+        <v>323</v>
       </c>
       <c r="F28" t="n">
-        <v>-35316</v>
+        <v>222</v>
       </c>
       <c r="G28" t="n">
-        <v>-30945</v>
+        <v>-350</v>
       </c>
       <c r="H28" t="n">
-        <v>-19767</v>
+        <v>-115</v>
       </c>
       <c r="I28" t="n">
-        <v>-11099</v>
+        <v>-9</v>
       </c>
       <c r="J28" t="n">
-        <v>-5224</v>
+        <v>-182</v>
       </c>
       <c r="K28" t="n">
-        <v>-10516</v>
+        <v>-231</v>
       </c>
       <c r="L28" t="n">
-        <v>-15076</v>
+        <v>122</v>
       </c>
       <c r="M28" t="n">
-        <v>-17223</v>
+        <v>-101</v>
       </c>
       <c r="N28" t="n">
-        <v>-10660</v>
+        <v>-46</v>
       </c>
       <c r="O28" t="n">
-        <v>-28986</v>
+        <v>-16</v>
       </c>
       <c r="P28" t="n">
-        <v>-13734</v>
+        <v>-13</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5185</v>
+        <v>-13</v>
       </c>
       <c r="R28" t="n">
-        <v>-7085</v>
+        <v>32</v>
       </c>
       <c r="S28" t="n">
-        <v>-4174</v>
+        <v>124</v>
       </c>
       <c r="T28" t="n">
-        <v>-2022</v>
+        <v>114</v>
+      </c>
+      <c r="U28" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>9414</v>
       </c>
       <c r="C29" t="n">
-        <v>252</v>
+        <v>-6553</v>
       </c>
       <c r="D29" t="n">
-        <v>243</v>
+        <v>-45519</v>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>-35472</v>
       </c>
       <c r="F29" t="n">
-        <v>-72</v>
+        <v>-19495</v>
       </c>
       <c r="G29" t="n">
-        <v>-440</v>
+        <v>-35316</v>
       </c>
       <c r="H29" t="n">
-        <v>-288</v>
+        <v>-30945</v>
       </c>
       <c r="I29" t="n">
-        <v>-283</v>
+        <v>-19767</v>
       </c>
       <c r="J29" t="n">
-        <v>71</v>
+        <v>-11099</v>
       </c>
       <c r="K29" t="n">
-        <v>85</v>
+        <v>-5224</v>
       </c>
       <c r="L29" t="n">
-        <v>-1063</v>
+        <v>-10516</v>
       </c>
       <c r="M29" t="n">
-        <v>-698</v>
+        <v>-15076</v>
       </c>
       <c r="N29" t="n">
-        <v>-149</v>
+        <v>-17223</v>
       </c>
       <c r="O29" t="n">
-        <v>-344</v>
+        <v>-10660</v>
       </c>
       <c r="P29" t="n">
-        <v>-129</v>
+        <v>-28986</v>
       </c>
       <c r="Q29" t="n">
-        <v>-246</v>
+        <v>-13734</v>
       </c>
       <c r="R29" t="n">
-        <v>-36</v>
+        <v>-5185</v>
       </c>
       <c r="S29" t="n">
-        <v>-127</v>
+        <v>-7085</v>
       </c>
       <c r="T29" t="n">
-        <v>-222</v>
+        <v>-4174</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-2022</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-7998</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-33497</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>-31610</v>
+        <v>252</v>
       </c>
       <c r="E30" t="n">
-        <v>-15367</v>
+        <v>243</v>
       </c>
       <c r="F30" t="n">
-        <v>2300</v>
+        <v>112</v>
       </c>
       <c r="G30" t="n">
-        <v>-9801</v>
+        <v>-72</v>
       </c>
       <c r="H30" t="n">
-        <v>-9543</v>
+        <v>-440</v>
       </c>
       <c r="I30" t="n">
-        <v>22304</v>
+        <v>-288</v>
       </c>
       <c r="J30" t="n">
-        <v>14208</v>
+        <v>-283</v>
       </c>
       <c r="K30" t="n">
-        <v>-3176</v>
+        <v>71</v>
       </c>
       <c r="L30" t="n">
-        <v>-1614</v>
+        <v>85</v>
       </c>
       <c r="M30" t="n">
-        <v>-3387</v>
+        <v>-1063</v>
       </c>
       <c r="N30" t="n">
-        <v>-1512</v>
+        <v>-698</v>
       </c>
       <c r="O30" t="n">
-        <v>-3150</v>
+        <v>-149</v>
       </c>
       <c r="P30" t="n">
-        <v>-1443</v>
+        <v>-344</v>
       </c>
       <c r="Q30" t="n">
-        <v>1937</v>
+        <v>-129</v>
       </c>
       <c r="R30" t="n">
-        <v>-7300</v>
+        <v>-246</v>
       </c>
       <c r="S30" t="n">
-        <v>2290</v>
+        <v>-36</v>
       </c>
       <c r="T30" t="n">
-        <v>4648</v>
+        <v>-127</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39100</v>
+        <v>-9829</v>
       </c>
       <c r="C31" t="n">
-        <v>45438</v>
+        <v>-7998</v>
       </c>
       <c r="D31" t="n">
-        <v>45438</v>
+        <v>-33497</v>
       </c>
       <c r="E31" t="n">
-        <v>45438</v>
+        <v>-31610</v>
       </c>
       <c r="F31" t="n">
-        <v>42827</v>
+        <v>-15367</v>
       </c>
       <c r="G31" t="n">
-        <v>42827</v>
+        <v>2300</v>
       </c>
       <c r="H31" t="n">
-        <v>42827</v>
+        <v>-9801</v>
       </c>
       <c r="I31" t="n">
-        <v>15596</v>
+        <v>-9543</v>
       </c>
       <c r="J31" t="n">
-        <v>15596</v>
+        <v>22304</v>
       </c>
       <c r="K31" t="n">
-        <v>15596</v>
+        <v>14208</v>
       </c>
       <c r="L31" t="n">
-        <v>16865</v>
+        <v>-3176</v>
       </c>
       <c r="M31" t="n">
-        <v>16865</v>
+        <v>-1614</v>
       </c>
       <c r="N31" t="n">
-        <v>16865</v>
+        <v>-3387</v>
       </c>
       <c r="O31" t="n">
-        <v>17954</v>
+        <v>-1512</v>
       </c>
       <c r="P31" t="n">
-        <v>17954</v>
+        <v>-3150</v>
       </c>
       <c r="Q31" t="n">
-        <v>17954</v>
+        <v>-1443</v>
       </c>
       <c r="R31" t="n">
-        <v>19279</v>
+        <v>1937</v>
       </c>
       <c r="S31" t="n">
-        <v>19279</v>
+        <v>-7300</v>
       </c>
       <c r="T31" t="n">
-        <v>19279</v>
+        <v>2290</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4648</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, at Carrying Value</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23426</v>
+        <v>39100</v>
       </c>
       <c r="C32" t="n">
-        <v>10187</v>
+        <v>39100</v>
       </c>
       <c r="D32" t="n">
-        <v>12005</v>
+        <v>45438</v>
       </c>
       <c r="E32" t="n">
-        <v>28750</v>
+        <v>45438</v>
       </c>
       <c r="F32" t="n">
-        <v>43852</v>
+        <v>45438</v>
       </c>
       <c r="G32" t="n">
-        <v>32045</v>
+        <v>42827</v>
       </c>
       <c r="H32" t="n">
-        <v>32307</v>
+        <v>42827</v>
       </c>
       <c r="I32" t="n">
-        <v>36890</v>
+        <v>42827</v>
       </c>
       <c r="J32" t="n">
-        <v>28785</v>
+        <v>15596</v>
       </c>
       <c r="K32" t="n">
-        <v>11551</v>
+        <v>15596</v>
       </c>
       <c r="L32" t="n">
-        <v>14308</v>
+        <v>15596</v>
       </c>
       <c r="M32" t="n">
-        <v>12681</v>
+        <v>16865</v>
       </c>
       <c r="N32" t="n">
-        <v>14886</v>
+        <v>16865</v>
       </c>
       <c r="O32" t="n">
-        <v>14496</v>
+        <v>16865</v>
       </c>
       <c r="P32" t="n">
-        <v>16186</v>
+        <v>17954</v>
       </c>
       <c r="Q32" t="n">
-        <v>19513</v>
+        <v>17954</v>
       </c>
       <c r="R32" t="n">
-        <v>11617</v>
+        <v>17954</v>
       </c>
       <c r="S32" t="n">
-        <v>21045</v>
+        <v>19279</v>
       </c>
       <c r="T32" t="n">
-        <v>23618</v>
+        <v>19279</v>
+      </c>
+      <c r="U32" t="n">
+        <v>19279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Paid, Net</t>
+          <t>Cash and Cash Equivalents, at Carrying Value</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>541</v>
+        <v>15462</v>
       </c>
       <c r="C33" t="n">
-        <v>6293</v>
+        <v>23426</v>
       </c>
       <c r="D33" t="n">
-        <v>5544</v>
+        <v>10187</v>
       </c>
       <c r="E33" t="n">
-        <v>448</v>
+        <v>12005</v>
       </c>
       <c r="F33" t="n">
-        <v>8326</v>
+        <v>28750</v>
       </c>
       <c r="G33" t="n">
-        <v>6559</v>
+        <v>43852</v>
       </c>
       <c r="H33" t="n">
-        <v>630</v>
+        <v>32045</v>
       </c>
       <c r="I33" t="n">
-        <v>2016</v>
+        <v>32307</v>
       </c>
       <c r="J33" t="n">
-        <v>1507</v>
+        <v>36890</v>
       </c>
       <c r="K33" t="n">
-        <v>405</v>
+        <v>28785</v>
       </c>
       <c r="L33" t="n">
-        <v>4647</v>
+        <v>11551</v>
       </c>
       <c r="M33" t="n">
-        <v>2641</v>
+        <v>14308</v>
       </c>
       <c r="N33" t="n">
-        <v>502</v>
+        <v>12681</v>
       </c>
       <c r="O33" t="n">
-        <v>7919</v>
+        <v>14886</v>
       </c>
       <c r="P33" t="n">
-        <v>6294</v>
+        <v>14496</v>
       </c>
       <c r="Q33" t="n">
-        <v>2907</v>
+        <v>16186</v>
       </c>
       <c r="R33" t="n">
-        <v>3122</v>
+        <v>19513</v>
       </c>
       <c r="S33" t="n">
-        <v>1250</v>
+        <v>11617</v>
       </c>
       <c r="T33" t="n">
-        <v>209</v>
+        <v>21045</v>
+      </c>
+      <c r="U33" t="n">
+        <v>23618</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
+          <t>Income Taxes Paid, Net</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>284</v>
+        <v>1999</v>
       </c>
       <c r="C34" t="n">
-        <v>603</v>
+        <v>541</v>
       </c>
       <c r="D34" t="n">
-        <v>478</v>
+        <v>6293</v>
       </c>
       <c r="E34" t="n">
-        <v>352</v>
+        <v>5544</v>
       </c>
       <c r="F34" t="n">
-        <v>356</v>
+        <v>448</v>
       </c>
       <c r="G34" t="n">
-        <v>245</v>
+        <v>8326</v>
       </c>
       <c r="H34" t="n">
-        <v>121</v>
+        <v>6559</v>
       </c>
       <c r="I34" t="n">
-        <v>302</v>
+        <v>630</v>
       </c>
       <c r="J34" t="n">
-        <v>182</v>
+        <v>2016</v>
       </c>
       <c r="K34" t="n">
-        <v>182</v>
+        <v>1507</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4647</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2641</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7919</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6294</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2907</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3122</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1250</v>
+      </c>
+      <c r="U34" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Capital Expenditures Incurred but Not yet Paid</t>
+          <t>Interest Paid, Excluding Capitalized Interest, Operating Activities</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16040</v>
+        <v>1097</v>
       </c>
       <c r="C35" t="n">
-        <v>9136</v>
+        <v>284</v>
       </c>
       <c r="D35" t="n">
-        <v>10618</v>
+        <v>603</v>
       </c>
       <c r="E35" t="n">
-        <v>9338</v>
+        <v>478</v>
       </c>
       <c r="F35" t="n">
-        <v>7217</v>
+        <v>352</v>
       </c>
       <c r="G35" t="n">
-        <v>3229</v>
+        <v>356</v>
       </c>
       <c r="H35" t="n">
-        <v>4217</v>
+        <v>245</v>
       </c>
       <c r="I35" t="n">
-        <v>4506</v>
+        <v>121</v>
       </c>
       <c r="J35" t="n">
-        <v>3845</v>
+        <v>302</v>
       </c>
       <c r="K35" t="n">
-        <v>4466</v>
+        <v>182</v>
       </c>
       <c r="L35" t="n">
-        <v>4130</v>
+        <v>182</v>
       </c>
       <c r="M35" t="n">
-        <v>4543</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3709</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2635</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2249</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2198</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2137</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1592</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1603</v>
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Acquisition Of Business And Intangible Assets</t>
+          <t>Capital Expenditures Incurred but Not yet Paid</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2169</v>
+        <v>19502</v>
       </c>
       <c r="C36" t="n">
-        <v>1931</v>
+        <v>16040</v>
       </c>
       <c r="D36" t="n">
-        <v>132</v>
+        <v>9136</v>
       </c>
       <c r="E36" t="n">
-        <v>159</v>
+        <v>10618</v>
       </c>
       <c r="F36" t="n">
-        <v>186</v>
+        <v>9338</v>
       </c>
       <c r="G36" t="n">
-        <v>267</v>
+        <v>7217</v>
       </c>
       <c r="H36" t="n">
-        <v>116</v>
+        <v>3229</v>
       </c>
       <c r="I36" t="n">
-        <v>182</v>
+        <v>4217</v>
       </c>
       <c r="J36" t="n">
-        <v>217</v>
+        <v>4506</v>
       </c>
       <c r="K36" t="n">
-        <v>263</v>
+        <v>3845</v>
       </c>
       <c r="L36" t="n">
-        <v>294</v>
+        <v>4466</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4130</v>
       </c>
       <c r="N36" t="n">
-        <v>73</v>
+        <v>4543</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3709</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2635</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2249</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2198</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2137</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1592</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1603</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Repurchase Of Common Stock In Accrued Expenses And Other Current Liabilities</t>
+          <t>Acquisition Of Business And Intangible Assets</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>2172</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2169</v>
       </c>
       <c r="D37" t="n">
-        <v>131</v>
+        <v>1931</v>
       </c>
       <c r="E37" t="n">
-        <v>577</v>
+        <v>132</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="I37" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="K37" t="n">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="L37" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M37" t="n">
-        <v>70</v>
+        <v>294</v>
       </c>
       <c r="N37" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -5758,29 +6004,32 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Equity Securities, FV-NI, Unrealized Gain (Loss)</t>
+          <t>Repurchase Of Common Stock In Accrued Expenses And Other Current Liabilities</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-548</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -5792,22 +6041,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -5822,13 +6071,16 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Long-term Debt</t>
+          <t>Equity Securities, FV-NI, Unrealized Gain (Loss)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5838,13 +6090,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>-548</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="F39" t="n">
-        <v>10432</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -5853,16 +6105,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>8455</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>8455</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>9921</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5886,6 +6138,9 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5908,29 +6163,29 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>288</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>280</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>240</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>1342</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>1002</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>770</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>413</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -5950,6 +6205,9 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5975,38 +6233,38 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>100</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>84</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>152</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>165</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>224</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>943</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>797</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>294</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>195</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>201</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6014,6 +6272,9 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6045,39 +6306,42 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>-347</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>-356</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>-240</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>-12</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>-33</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>-105</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>-163</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>-133</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>-72</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>-100</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-158</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-169</v>
       </c>
     </row>
@@ -6109,26 +6373,26 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>148</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>101</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>19</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>190</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>170</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>126</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
@@ -6142,6 +6406,9 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6182,30 +6449,33 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>9333</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>7713</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>5065</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>15331</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>6337</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>1650</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>9779</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>5381</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>2764</v>
       </c>
     </row>
@@ -6246,30 +6516,33 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>-250</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>-59</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>20</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>15</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>3</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>-50</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>-24</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-17</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -6310,30 +6583,33 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>-35</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>-28</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>-52</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>87</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>6</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>111</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-1</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>-16</v>
       </c>
     </row>
